--- a/hiragana_questions.xlsx
+++ b/hiragana_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ri2510027\Desktop\算数ウェブアプリ関連\ひらがな\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18004A5B-A74A-4B5E-90D8-30DFDAD1EDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7169AE7F-3EC8-48C9-B9C0-DBDD5D5698A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題リスト" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="717">
   <si>
     <t>ID</t>
   </si>
@@ -1978,43 +1978,25 @@
     <t>4-23</t>
   </si>
   <si>
-    <t>ありがとう</t>
-  </si>
-  <si>
-    <t>めりがとう</t>
-  </si>
-  <si>
-    <t>ありがどつ</t>
-  </si>
-  <si>
-    <t>ありかとう</t>
-  </si>
-  <si>
-    <t>ありがとつ</t>
-  </si>
-  <si>
-    <t>ありらとう</t>
-  </si>
-  <si>
     <t>4-24</t>
   </si>
   <si>
-    <t>たからばこ</t>
-  </si>
-  <si>
-    <t>だからばこ</t>
-  </si>
-  <si>
-    <t>たがらばこ</t>
-  </si>
-  <si>
-    <t>たからぱこ</t>
-  </si>
-  <si>
-    <t>たからばご</t>
-  </si>
-  <si>
-    <t>たからはこ</t>
+    <t>とびばこ</t>
+  </si>
+  <si>
+    <t>とひばこ</t>
+  </si>
+  <si>
+    <t>とびはこ</t>
+  </si>
+  <si>
+    <t>とびばご</t>
+  </si>
+  <si>
+    <t>こびばこ</t>
+  </si>
+  <si>
+    <t>とびぱこ</t>
   </si>
   <si>
     <t>4-25</t>
@@ -2083,22 +2065,7 @@
     <t>4-28</t>
   </si>
   <si>
-    <t>かたつむり</t>
-  </si>
-  <si>
-    <t>がたつむり</t>
-  </si>
-  <si>
-    <t>かだつむり</t>
-  </si>
-  <si>
-    <t>かたづむり</t>
-  </si>
-  <si>
-    <t>かたつぬり</t>
-  </si>
-  <si>
-    <t>かたつむし</t>
+    <t>はねがき</t>
   </si>
   <si>
     <t>4-29</t>
@@ -2204,27 +2171,21 @@
   </si>
   <si>
     <t>らくだ</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>うくだ</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>らくた</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>らぐだ</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>うぐだ</t>
-    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>らくち</t>
-    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -2325,7 +2286,7 @@
         <color rgb="FF991B1B"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFECACA"/>
         </patternFill>
       </fill>
@@ -6367,31 +6328,31 @@
         <v>287</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>22</v>
@@ -7627,31 +7588,31 @@
         <v>492</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>650</v>
+        <v>610</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>651</v>
+        <v>606</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>652</v>
+        <v>609</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>22</v>
@@ -7666,37 +7627,37 @@
     </row>
     <row r="115" spans="1:14" ht="28.5">
       <c r="A115" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>22</v>
@@ -7711,37 +7672,37 @@
     </row>
     <row r="116" spans="1:14" ht="28.5">
       <c r="A116" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>22</v>
@@ -7756,37 +7717,37 @@
     </row>
     <row r="117" spans="1:14" ht="28.5">
       <c r="A117" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>22</v>
@@ -7801,37 +7762,37 @@
     </row>
     <row r="118" spans="1:14" ht="28.5">
       <c r="A118" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>22</v>
@@ -7846,37 +7807,37 @@
     </row>
     <row r="119" spans="1:14" ht="28.5">
       <c r="A119" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>682</v>
+        <v>556</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>683</v>
+        <v>557</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>684</v>
+        <v>558</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>685</v>
+        <v>559</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>686</v>
+        <v>560</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>22</v>
@@ -7891,37 +7852,37 @@
     </row>
     <row r="120" spans="1:14" ht="28.5">
       <c r="A120" s="2" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>22</v>
@@ -7936,37 +7897,37 @@
     </row>
     <row r="121" spans="1:14" ht="28.5">
       <c r="A121" s="2" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>492</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>22</v>
@@ -8012,7 +7973,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="4" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="B1" s="5"/>
     </row>
@@ -8022,13 +7983,13 @@
     </row>
     <row r="3" spans="1:2" ht="71.25">
       <c r="A3" s="2" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:2" ht="71.25">
       <c r="A4" s="2" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="B4" s="2"/>
     </row>
@@ -8038,43 +7999,43 @@
     </row>
     <row r="6" spans="1:2" ht="18">
       <c r="A6" s="3" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" ht="42.75">
       <c r="A7" s="2" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" ht="42.75">
       <c r="A8" s="2" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2" ht="42.75">
       <c r="A9" s="2" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:2" ht="85.5">
       <c r="A10" s="2" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2" ht="57">
       <c r="A11" s="2" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2" ht="57">
       <c r="A12" s="2" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="B12" s="2"/>
     </row>
@@ -8084,7 +8045,7 @@
     </row>
     <row r="14" spans="1:2" ht="18">
       <c r="A14" s="3" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -8093,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -8101,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -8109,15 +8070,15 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8125,7 +8086,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8133,7 +8094,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>
@@ -8158,7 +8119,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8195,7 +8156,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="B6">
         <v>120</v>
